--- a/data/trans_bre/P1428-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1428-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,95</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>167,54%</t>
+          <t>165,44%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 12,46</t>
+          <t>2,36; 12,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 7,98</t>
+          <t>-0,16; 8,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 8,23</t>
+          <t>-1,21; 8,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 7,87</t>
+          <t>1,93; 7,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,08; 315,77</t>
+          <t>21,54; 285,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 318,49</t>
+          <t>-10,53; 320,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,22; 212,34</t>
+          <t>-20,74; 228,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43,68; 426,84</t>
+          <t>40,12; 409,4</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,33</t>
+          <t>5,16</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>138,02%</t>
+          <t>134,08%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,45; 17,72</t>
+          <t>9,54; 17,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 9,67</t>
+          <t>3,47; 9,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 9,29</t>
+          <t>3,35; 9,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 8,1</t>
+          <t>2,68; 7,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>171,63; 540,64</t>
+          <t>150,57; 537,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,25; 573,66</t>
+          <t>66,36; 506,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,89; 449,35</t>
+          <t>78,5; 440,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,11; 319,59</t>
+          <t>47,99; 311,79</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,79</t>
+          <t>9,92</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>158,76%</t>
+          <t>165,7%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,08; 19,5</t>
+          <t>10,11; 19,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 12,38</t>
+          <t>2,78; 12,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 7,66</t>
+          <t>0,38; 7,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 13,43</t>
+          <t>6,36; 13,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>188,66; 808,42</t>
+          <t>195,86; 876,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,05; 234,89</t>
+          <t>29,39; 248,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 323,85</t>
+          <t>3,88; 295,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>62,65; 280,44</t>
+          <t>79,52; 297,94</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,29</t>
+          <t>13,94</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>100,62%</t>
+          <t>164,44%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,06; 15,14</t>
+          <t>6,24; 15,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 11,13</t>
+          <t>3,21; 10,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 13,13</t>
+          <t>4,75; 13,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 15,04</t>
+          <t>9,35; 18,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>68,31; 321,3</t>
+          <t>69,66; 323,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,15; 395,16</t>
+          <t>49,59; 388,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,11; 487,59</t>
+          <t>70,78; 496,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,98; 200,14</t>
+          <t>80,65; 289,1</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,14</t>
+          <t>12,56</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>241,5%</t>
+          <t>237,65%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,65; 19,47</t>
+          <t>5,52; 19,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,32; 16,01</t>
+          <t>4,6; 16,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 12,18</t>
+          <t>2,11; 11,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,94; 17,53</t>
+          <t>8,21; 16,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,59; 407,33</t>
+          <t>47,31; 394,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,77; 526,1</t>
+          <t>54,29; 527,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,87; 782,88</t>
+          <t>23,21; 829,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>104,12; 460,02</t>
+          <t>101,49; 461,62</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,14</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>118,02%</t>
+          <t>120,72%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,79; 15,99</t>
+          <t>5,26; 15,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,36; 15,64</t>
+          <t>2,7; 14,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,28; 13,81</t>
+          <t>3,97; 14,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,73; 14,25</t>
+          <t>5,84; 14,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>53,32; 347,42</t>
+          <t>61,23; 373,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,97; 184,9</t>
+          <t>15,27; 166,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60,82; 481,86</t>
+          <t>50,54; 522,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53,49; 211,5</t>
+          <t>54,79; 221,82</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29,37</t>
+          <t>9,4</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>442,15%</t>
+          <t>146,37%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 10,12</t>
+          <t>2,91; 9,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,15; 12,9</t>
+          <t>6,0; 12,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 7,1</t>
+          <t>1,89; 6,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,15; 62,04</t>
+          <t>6,16; 12,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,63; 155,27</t>
+          <t>28,47; 153,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,56; 270,34</t>
+          <t>79,45; 266,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,69; 264,7</t>
+          <t>39,96; 270,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>113,48; 1179,96</t>
+          <t>77,77; 249,65</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10,6</t>
+          <t>8,88</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>444,87%</t>
+          <t>277,43%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,3; 13,26</t>
+          <t>6,11; 13,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,18</t>
+          <t>3,08; 8,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,29; 8,13</t>
+          <t>3,44; 8,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,13; 13,6</t>
+          <t>6,66; 11,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>51,02; 154,93</t>
+          <t>45,87; 144,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,36; 312,58</t>
+          <t>64,39; 328,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,89; 455,19</t>
+          <t>80,72; 473,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>232,61; 1103,97</t>
+          <t>159,09; 465,33</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14,1</t>
+          <t>9,13</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>280,35%</t>
+          <t>173,83%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,85; 11,96</t>
+          <t>8,87; 12,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,92; 8,63</t>
+          <t>5,94; 8,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,99</t>
+          <t>4,65; 7,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,8; 30,46</t>
+          <t>8,03; 10,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>114,3; 185,56</t>
+          <t>112,27; 182,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>101,08; 188,81</t>
+          <t>101,4; 191,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>112,28; 221,45</t>
+          <t>112,97; 224,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>165,41; 597,11</t>
+          <t>138,57; 214,2</t>
         </is>
       </c>
     </row>
